--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,184 +656,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>700</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E12" s="3">
         <v>107700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>98000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>68900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>66100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>69500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>61000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>56500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>53700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>46500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>40900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>37000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>34900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>27500</v>
       </c>
       <c r="S12" s="3">
         <v>27500</v>
       </c>
       <c r="T12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="U12" s="3">
         <v>64300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>18200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>32900</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1214,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1285,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E17" s="3">
         <v>123200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>112600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>82200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>77000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>79900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>71200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>65500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>62400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>53200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>72500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>38500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-180000</v>
       </c>
       <c r="E18" s="3">
+        <v>-123200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-108800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-75200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-61700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-76500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-62100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-57900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-52900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-53200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-34000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-34500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-28700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,34 +1510,35 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>19100</v>
       </c>
       <c r="E20" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F20" s="3">
         <v>10500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
@@ -1514,125 +1547,131 @@
         <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-159300</v>
       </c>
       <c r="E21" s="3">
+        <v>-110800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-96800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-66600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-55200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-72400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-60000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-56500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-51600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-51900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-43200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-26300</v>
       </c>
       <c r="Q21" s="3">
         <v>-26300</v>
       </c>
       <c r="R21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="S21" s="3">
         <v>-19300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-30500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-29300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>300</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1674,117 +1713,123 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-161200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-112300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-98300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-68100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-56600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-73600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-61200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-57600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-52700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-52900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-44300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-30500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1797,27 +1842,27 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4400</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1833,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-108400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-98300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-68100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-56500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-73300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-61200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-57600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-52900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-44300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-27200</v>
       </c>
       <c r="Q26" s="3">
         <v>-27200</v>
       </c>
       <c r="R26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-19500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-30500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-108400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-98300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-68100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-56500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-73300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-61200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-57600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-52700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-52900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-44300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-27200</v>
       </c>
       <c r="Q27" s="3">
         <v>-27200</v>
       </c>
       <c r="R27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="S27" s="3">
         <v>-21700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-43100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-35000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,34 +2396,37 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-19100</v>
       </c>
       <c r="E32" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
@@ -2366,114 +2435,120 @@
         <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-108400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-98300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-68100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-56500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-73300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-61200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-57600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-52700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-52900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-44300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-27200</v>
       </c>
       <c r="Q33" s="3">
         <v>-27200</v>
       </c>
       <c r="R33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="S33" s="3">
         <v>-21700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-43100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-35000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-108400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-98300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-68100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-56500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-73300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-61200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-57600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-52700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-52900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-44300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-27200</v>
       </c>
       <c r="Q35" s="3">
         <v>-27200</v>
       </c>
       <c r="R35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="S35" s="3">
         <v>-21700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-43100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-35000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,65 +2829,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>696100</v>
+      </c>
+      <c r="E41" s="3">
         <v>358400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>380300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>427200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>161400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>178900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>108500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>195600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>351600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>64900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>182700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,65 +2901,68 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1156800</v>
+      </c>
+      <c r="E42" s="3">
         <v>454800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>529200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>482600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>483500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>476100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>355700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>421100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>468600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>479500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>450700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>330000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>336500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>401300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>301500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>165300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>106100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>114500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,65 +2975,68 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3028,65 +3123,68 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E45" s="3">
         <v>11000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>8200</v>
       </c>
       <c r="N45" s="3">
         <v>8200</v>
       </c>
       <c r="O45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,65 +3197,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1879300</v>
+      </c>
+      <c r="E46" s="3">
         <v>824500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>922100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>922800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>660200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>675100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>483000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>534300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>589800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>623500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>661000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>697400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>454100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>482900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>340400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>362100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>134000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>149100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3241,65 +3345,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E48" s="3">
         <v>73400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>72800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>71600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>71200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,65 +3419,68 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E49" s="3">
         <v>72600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>74200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>75000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>76100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>76400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>76600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76900</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3383,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,65 +3641,68 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E52" s="3">
         <v>13700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1300</v>
       </c>
       <c r="M52" s="3">
         <v>1300</v>
       </c>
       <c r="N52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="O52" s="3">
         <v>1400</v>
       </c>
       <c r="P52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,65 +3789,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2061700</v>
+      </c>
+      <c r="E54" s="3">
         <v>984200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1073700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1073200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>811900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>825900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>632800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>682800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>738000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>735000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>774000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>811700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>567400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>595100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>454000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>454300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>220500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>234700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,65 +3921,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E57" s="3">
         <v>29600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3901,17 +4034,17 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
-        <v>100</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
@@ -3919,8 +4052,8 @@
       <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>200</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -3934,65 +4067,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E59" s="3">
         <v>55900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>46300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>35400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>35700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>33500</v>
       </c>
       <c r="R59" s="3">
         <v>33500</v>
       </c>
       <c r="S59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="T59" s="3">
         <v>31500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,65 +4141,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>143900</v>
+      </c>
+      <c r="E60" s="3">
         <v>85500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>62000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>63500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>57500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>60400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>42400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,8 +4215,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4147,65 +4289,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E62" s="3">
         <v>61200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>64800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>71200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>70400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>74300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>75100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>43200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>49700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>30400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,65 +4585,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E66" s="3">
         <v>146800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>142900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>121000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>126700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>144500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>134000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>131800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>135400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>96800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>89000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>89100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>92700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>93500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>69000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4722,13 +4889,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>305100</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -4742,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,65 +4983,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1137700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-976200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-867700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-769400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-701300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-644800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-571500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-510300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-452600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-400000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-347000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-302700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-265500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-231300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-204100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-176900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-157400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-142800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,65 +5279,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1826200</v>
+      </c>
+      <c r="E76" s="3">
         <v>837500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>930800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>952200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>685200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>681400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>498800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>551000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>602600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>638200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>685000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>722600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>474700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>505100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>360500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>385300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-152600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-139400</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-108400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-98300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-68100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-56500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-73300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-61200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-57600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-52700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-52900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-44300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-27200</v>
       </c>
       <c r="Q81" s="3">
         <v>-27200</v>
       </c>
       <c r="R81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="S81" s="3">
         <v>-21700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-43100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-35000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,13 +5610,14 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
         <v>1500</v>
@@ -5428,19 +5626,19 @@
         <v>1500</v>
       </c>
       <c r="G83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H83" s="3">
         <v>1400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1200</v>
       </c>
       <c r="J83" s="3">
         <v>1200</v>
       </c>
       <c r="K83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="L83" s="3">
         <v>1100</v>
@@ -5449,7 +5647,7 @@
         <v>1100</v>
       </c>
       <c r="N83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="O83" s="3">
         <v>900</v>
@@ -5467,25 +5665,28 @@
         <v>900</v>
       </c>
       <c r="T83" s="3">
+        <v>900</v>
+      </c>
+      <c r="U83" s="3">
         <v>2500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-120600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-67100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-62400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-61800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-51700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-55700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-55200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-39300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-36600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-34100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-38000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6156,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-380400</v>
+      </c>
+      <c r="E94" s="3">
         <v>77400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-43500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-123400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>62400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>44000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>8500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-122800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>62900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-136500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-59700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>8000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-110000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,79 +6774,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>839400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>64600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>324200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>51400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>248300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>282300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>168900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>253700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>4200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>56600</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6674,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>338400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-46000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>265800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>73200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-66400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-156000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>247300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-157800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>166000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-47800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>68300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,190 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>3800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9800</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,8 +919,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E12" s="3">
         <v>148500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>107700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>98000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>68900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>66100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>69500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>61000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>56500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>53700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>46500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>37000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>32900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>27500</v>
       </c>
       <c r="T12" s="3">
         <v>27500</v>
       </c>
       <c r="U12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="V12" s="3">
         <v>64300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>18200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>32900</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,31 +1179,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>2800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E17" s="3">
         <v>180700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>123200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>112600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>82200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>77000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>79900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>71200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>65500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>62400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>53200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>72500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>38500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-180000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-123200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-108800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-75200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-61700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-76500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-62100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-57900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-52900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-53200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-44500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-27500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-34500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-28700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,37 +1544,38 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>19100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
@@ -1550,131 +1584,137 @@
         <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-159300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-110800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-96800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-66600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-55200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-72400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-60000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-56500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-51600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-51900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-43200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-26300</v>
       </c>
       <c r="R21" s="3">
         <v>-26300</v>
       </c>
       <c r="S21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="T21" s="3">
         <v>-19300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-30500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-29300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1716,123 +1756,129 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-161200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-112300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-98300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-68100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-56600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-73600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-61200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-57600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-52700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-52900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-44300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1845,27 +1891,27 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4400</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-161500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-108400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-98300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-68100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-73300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-61200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-57600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-52700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-44300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-27200</v>
       </c>
       <c r="R26" s="3">
         <v>-27200</v>
       </c>
       <c r="S26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="T26" s="3">
         <v>-19500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-33100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-161500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-108400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-98300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-68100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-56500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-73300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-61200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-57600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-52700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-44300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-27200</v>
       </c>
       <c r="R27" s="3">
         <v>-27200</v>
       </c>
       <c r="S27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="T27" s="3">
         <v>-21700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-43100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-13900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,37 +2466,40 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-19100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
@@ -2438,117 +2508,123 @@
         <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-161500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-108400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-98300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-68100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-56500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-73300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-61200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-57600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-52700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-44300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-27200</v>
       </c>
       <c r="R33" s="3">
         <v>-27200</v>
       </c>
       <c r="S33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="T33" s="3">
         <v>-21700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-43100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-13900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-161500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-108400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-98300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-68100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-56500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-73300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-61200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-57600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-52700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-44300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-27200</v>
       </c>
       <c r="R35" s="3">
         <v>-27200</v>
       </c>
       <c r="S35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="T35" s="3">
         <v>-21700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-43100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-13900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,68 +2916,69 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E41" s="3">
         <v>696100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>358400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>380300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>427200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>161400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>178900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>108500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>195600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>351600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>64900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>182700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,68 +2991,71 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1415100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1156800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>454800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>529200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>482600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>483500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>476100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>355700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>421100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>468600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>479500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>450700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>330000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>336500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>401300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>301500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>165300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>106100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>114500</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,68 +3068,71 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3126,68 +3222,71 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E45" s="3">
         <v>25100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>8200</v>
       </c>
       <c r="O45" s="3">
         <v>8200</v>
       </c>
       <c r="P45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,68 +3299,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1729200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1879300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>824500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>922100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>922800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>660200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>675100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>483000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>534300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>589800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>623500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>661000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>697400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>454100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>482900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>340400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>362100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>134000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>149100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,8 +3376,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3348,68 +3453,71 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E48" s="3">
         <v>100000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>74500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>71600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>71200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,68 +3530,71 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E49" s="3">
         <v>72300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>74000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>75800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>76100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>76400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,68 +3761,71 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E52" s="3">
         <v>10100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1300</v>
       </c>
       <c r="N52" s="3">
         <v>1300</v>
       </c>
       <c r="O52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="P52" s="3">
         <v>1400</v>
       </c>
       <c r="Q52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,68 +3915,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1908400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2061700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>984200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1073700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1073200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>811900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>825900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>632800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>682800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>738000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>735000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>774000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>811700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>567400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>595100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>454000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>454300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>220500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>234700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,68 +4052,69 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E57" s="3">
         <v>61800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4037,17 +4171,17 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>100</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
@@ -4055,8 +4189,8 @@
       <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>200</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4070,68 +4204,71 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E59" s="3">
         <v>82100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>49500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>46300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>35700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>33500</v>
       </c>
       <c r="S59" s="3">
         <v>33500</v>
       </c>
       <c r="T59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="U59" s="3">
         <v>31500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>32500</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,68 +4281,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E60" s="3">
         <v>143900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>85500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>62000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>73300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>63500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>60400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38600</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4358,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4292,68 +4435,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E62" s="3">
         <v>91700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>61200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>64800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>64800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>71200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>70400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>74300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>75100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>43200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>47600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>49700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>30400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,68 +4743,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E66" s="3">
         <v>235500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>142900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>121000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>126700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>144500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>134000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>131800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>135400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>96800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>89000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>92700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>93500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>68000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>69100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4892,13 +5060,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>305100</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,68 +5157,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1253700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-976200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-867700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-769400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-701300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-644800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-571500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-510300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-452600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-400000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-347000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-302700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-265500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-231300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-204100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-176900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-157400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-142800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,68 +5465,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1725500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1826200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>837500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>930800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>952200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>685200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>681400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>498800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>551000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>602600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>638200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>685000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>722600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>474700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>505100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>360500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>385300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-152600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-139400</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-161500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-108400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-98300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-68100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-56500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-73300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-61200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-57600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-52700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-44300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-27200</v>
       </c>
       <c r="R81" s="3">
         <v>-27200</v>
       </c>
       <c r="S81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="T81" s="3">
         <v>-21700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-43100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-13900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,16 +5809,17 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1500</v>
       </c>
       <c r="F83" s="3">
         <v>1500</v>
@@ -5629,19 +5828,19 @@
         <v>1500</v>
       </c>
       <c r="H83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1200</v>
       </c>
       <c r="K83" s="3">
         <v>1200</v>
       </c>
       <c r="L83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="M83" s="3">
         <v>1100</v>
@@ -5650,7 +5849,7 @@
         <v>1100</v>
       </c>
       <c r="O83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="P83" s="3">
         <v>900</v>
@@ -5668,25 +5867,28 @@
         <v>900</v>
       </c>
       <c r="U83" s="3">
+        <v>900</v>
+      </c>
+      <c r="V83" s="3">
         <v>2500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-160600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-120600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-67100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-62400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-61800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-51700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-55700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-55200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-34100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-27000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-28000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-38000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-380400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>77400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>62400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>44000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>8500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-122800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>62900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-101000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-136500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-59700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>8000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-110000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,82 +7020,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>839400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>64600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>324200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>51400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>248300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>282300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>168900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>253700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>4200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>56600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-407700</v>
+      </c>
+      <c r="E102" s="3">
         <v>338400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-46000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>265800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>73200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-66400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-156000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>247300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-157800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>166000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-47800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>68300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,120 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,76 +781,79 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>3800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9800</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -922,8 +929,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -999,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E12" s="3">
         <v>118000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>148500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>107700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>98000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>68900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>66100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>69500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>61000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>56500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>53700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>46500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>40900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>34900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>32900</v>
-      </c>
-      <c r="T12" s="3">
-        <v>27500</v>
       </c>
       <c r="U12" s="3">
         <v>27500</v>
       </c>
       <c r="V12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="W12" s="3">
         <v>64300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>18200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>32900</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,17 +1199,20 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>2800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1208,8 +1228,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,85 +1388,89 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E17" s="3">
         <v>143700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>180700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>123200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>112600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>82200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>77000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>79900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>71200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>65500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>62400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>31700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>72500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1448,76 +1478,79 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-180000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-123200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-108800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-75200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-61700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-76500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-62100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-57900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-52900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-53200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-44500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-34000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-27500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-34500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-28700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,8 +1578,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1554,31 +1588,31 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F20" s="3">
         <v>19100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>200</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
@@ -1587,43 +1621,46 @@
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1631,93 +1668,96 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-114200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-159300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-110800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-96800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-66600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-55200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-72400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-60000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-56500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-51600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-51900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-43200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-26300</v>
       </c>
       <c r="S21" s="3">
         <v>-26300</v>
       </c>
       <c r="T21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="U21" s="3">
         <v>-19300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-18100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-30500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-29300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1759,102 +1799,108 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-116000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-161200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-112300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-98300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-68100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-56600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-61200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-57600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-52700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-44300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-19000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-33100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1862,26 +1908,26 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3900</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1894,27 +1940,27 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4400</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-116000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-161500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-108400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-68100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-56500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-73300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-61200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-57600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-44300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-27200</v>
       </c>
       <c r="S26" s="3">
         <v>-27200</v>
       </c>
       <c r="T26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="U26" s="3">
         <v>-19500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-33100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-116000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-161500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-108400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-98300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-68100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-73300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-61200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-57600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-52900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-44300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-27200</v>
       </c>
       <c r="S27" s="3">
         <v>-27200</v>
       </c>
       <c r="T27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="U27" s="3">
         <v>-21700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-43100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,8 +2536,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2478,31 +2548,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-19100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-200</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
@@ -2511,120 +2581,126 @@
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-116000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-161500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-108400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-98300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-68100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-56500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-73300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-61200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-57600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-52900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-44300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-27200</v>
       </c>
       <c r="S33" s="3">
         <v>-27200</v>
       </c>
       <c r="T33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="U33" s="3">
         <v>-21700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-43100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-116000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-161500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-108400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-98300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-68100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-56500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-73300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-61200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-57600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-52900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-44300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-27200</v>
       </c>
       <c r="S35" s="3">
         <v>-27200</v>
       </c>
       <c r="T35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="U35" s="3">
         <v>-21700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-43100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,71 +3003,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>275700</v>
+      </c>
+      <c r="E41" s="3">
         <v>288400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>696100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>358400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>380300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>427200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>161400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>178900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>108500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>129200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>195600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>351600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>104300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>64900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>182700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21800</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,71 +3081,74 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1315000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1415100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1156800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>454800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>529200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>482600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>483500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>476100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>355700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>421100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>468600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>479500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>450700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>330000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>336500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>401300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>301500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>165300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>106100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>114500</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,8 +3161,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3080,62 +3173,62 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3241,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3225,71 +3321,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E45" s="3">
         <v>25700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>8200</v>
       </c>
       <c r="P45" s="3">
         <v>8200</v>
       </c>
       <c r="Q45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="R45" s="3">
         <v>7000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3900</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,71 +3401,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1624700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1729200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1879300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>824500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>922100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>922800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>660200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>675100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>483000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>534300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>589800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>623500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>661000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>697400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>454100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>482900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>340400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>362100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>134000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>149100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3481,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3456,71 +3561,74 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E48" s="3">
         <v>99900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>74500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>73300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>71600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,71 +3641,74 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E49" s="3">
         <v>72100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>75600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>76100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>76900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,71 +3881,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1300</v>
       </c>
       <c r="O52" s="3">
         <v>1300</v>
       </c>
       <c r="P52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Q52" s="3">
         <v>1400</v>
       </c>
       <c r="R52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,71 +4041,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1808400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1908400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2061700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>984200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1073700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1073200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>811900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>825900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>632800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>682800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>738000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>735000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>774000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>811700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>567400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>595100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>454000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>454300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>220500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>234700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,71 +4183,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E57" s="3">
         <v>32400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>61800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,8 +4261,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4174,17 +4308,17 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
-        <v>100</v>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
@@ -4192,8 +4326,8 @@
       <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>200</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4207,71 +4341,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E59" s="3">
         <v>61300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>49500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>46300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>35700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>33500</v>
       </c>
       <c r="T59" s="3">
         <v>33500</v>
       </c>
       <c r="U59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="V59" s="3">
         <v>31500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>32500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,71 +4421,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E60" s="3">
         <v>93700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>143900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>78100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>62000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>73300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>57500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>60400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>42400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>41500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,8 +4501,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4438,71 +4581,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E62" s="3">
         <v>89200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>91700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>61200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>64800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>71200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>70400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>74300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>75100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>27500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>30400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,71 +4901,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E66" s="3">
         <v>182900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>235500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>146800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>142900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>121000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>126700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>144500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>134000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>131800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>135400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>96800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>89100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>92700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5063,13 +5231,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>305100</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,71 +5331,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1386900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-976200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-867700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-769400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-701300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-644800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-571500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-510300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-452600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-400000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-347000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-302700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-265500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-231300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-204100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-176900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-157400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-142800</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,71 +5651,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1618800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1725500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1826200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>837500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>930800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>952200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>685200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>681400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>498800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>551000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>602600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>638200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>685000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>722600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>474700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>505100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>360500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>385300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-152600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-139400</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-116000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-161500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-108400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-98300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-68100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-56500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-73300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-61200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-57600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-52900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-44300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-27200</v>
       </c>
       <c r="S81" s="3">
         <v>-27200</v>
       </c>
       <c r="T81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="U81" s="3">
         <v>-21700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-43100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,19 +6008,20 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1500</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
@@ -5831,19 +6030,19 @@
         <v>1500</v>
       </c>
       <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1200</v>
       </c>
       <c r="L83" s="3">
         <v>1200</v>
       </c>
       <c r="M83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="N83" s="3">
         <v>1100</v>
@@ -5852,7 +6051,7 @@
         <v>1100</v>
       </c>
       <c r="P83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="Q83" s="3">
         <v>900</v>
@@ -5870,25 +6069,28 @@
         <v>900</v>
       </c>
       <c r="V83" s="3">
+        <v>900</v>
+      </c>
+      <c r="W83" s="3">
         <v>2500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-160600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-120600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-67100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-62400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-61800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-51700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-55700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-55200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-39300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-34100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-27000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-28000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-38000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13000</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,85 +6598,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6836,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-248000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-380400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>77400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-123400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>62400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>44000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>8500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-122800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>62900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-101000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-136500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-59700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>8000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-110000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,85 +7266,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>839400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>64600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>324200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>51400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>248300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>282300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>168900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>253700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>4200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>56600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-407700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>338400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-46000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>265800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>73200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-66400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-156000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>247300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>40900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-157800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>166000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-47800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>68300</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,227 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>38000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9800</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>118000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>136600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>68900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -932,31 +939,34 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-135800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-61900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>134900</v>
+        <v>138400</v>
       </c>
       <c r="E12" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F12" s="3">
         <v>118000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>148500</v>
       </c>
-      <c r="G12" s="3">
-        <v>107700</v>
-      </c>
       <c r="H12" s="3">
-        <v>98000</v>
+        <v>99600</v>
       </c>
       <c r="I12" s="3">
+        <v>90300</v>
+      </c>
+      <c r="J12" s="3">
         <v>68900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>66100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>69500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>61000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>56500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>53700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>46500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>45900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>37000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>27500</v>
       </c>
       <c r="V12" s="3">
         <v>27500</v>
       </c>
       <c r="W12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="X12" s="3">
         <v>64300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>18200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>32900</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,22 +1219,25 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>2800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>25500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1231,8 +1251,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1282,31 +1302,34 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E17" s="3">
         <v>156600</v>
       </c>
-      <c r="E17" s="3">
-        <v>143700</v>
-      </c>
       <c r="F17" s="3">
-        <v>180700</v>
+        <v>140900</v>
       </c>
       <c r="G17" s="3">
+        <v>155200</v>
+      </c>
+      <c r="H17" s="3">
         <v>123200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>112600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>82200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>77000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>71200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>62400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>42800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>72500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>38500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-175700</v>
       </c>
       <c r="E18" s="3">
-        <v>-143700</v>
+        <v>-156600</v>
       </c>
       <c r="F18" s="3">
-        <v>-180000</v>
+        <v>-140900</v>
       </c>
       <c r="G18" s="3">
+        <v>-154500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-123200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-108800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-75200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-61700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-76500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-62100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-57900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-52900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-53200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-34000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-21100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-19600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-34500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,43 +1612,44 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
-        <v>27700</v>
+        <v>-1900</v>
       </c>
       <c r="F20" s="3">
-        <v>19100</v>
+        <v>-3900</v>
       </c>
       <c r="G20" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>10500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
@@ -1624,123 +1658,129 @@
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>200</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-175100</v>
       </c>
       <c r="E21" s="3">
-        <v>-114200</v>
+        <v>-153000</v>
       </c>
       <c r="F21" s="3">
-        <v>-159300</v>
+        <v>-135400</v>
       </c>
       <c r="G21" s="3">
-        <v>-110800</v>
+        <v>-153100</v>
       </c>
       <c r="H21" s="3">
-        <v>-96800</v>
+        <v>-122000</v>
       </c>
       <c r="I21" s="3">
-        <v>-66600</v>
+        <v>-107500</v>
       </c>
       <c r="J21" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-55200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-72400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-60000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-56500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-51600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-51900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-36200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-26300</v>
       </c>
       <c r="T21" s="3">
         <v>-26300</v>
       </c>
       <c r="U21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="V21" s="3">
         <v>-19300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-18100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-30500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1750,20 +1790,20 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1802,135 +1842,141 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-133200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-116000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-161200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-112300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-98300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-68100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-56600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-73600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-61200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-57600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-52900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-37200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-19000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-33100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3900</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1943,27 +1989,27 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4400</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,8 +2025,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-133200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-116000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-161500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-108400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-98300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-68100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-56500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-73300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-61200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-57600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-52900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-37200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-27200</v>
       </c>
       <c r="T26" s="3">
         <v>-27200</v>
       </c>
       <c r="U26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="V26" s="3">
         <v>-19500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-133200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-116000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-161500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-108400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-98300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-68100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-56500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-73300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-57600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-52700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-52900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-27200</v>
       </c>
       <c r="T27" s="3">
         <v>-27200</v>
       </c>
       <c r="U27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="V27" s="3">
         <v>-21700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-18800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-43100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,43 +2606,46 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-27700</v>
+        <v>1900</v>
       </c>
       <c r="F32" s="3">
-        <v>-19100</v>
+        <v>3900</v>
       </c>
       <c r="G32" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
@@ -2584,123 +2654,129 @@
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1700</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-133200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-116000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-161500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-108400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-98300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-68100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-56500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-73300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-61200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-57600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-52700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-52900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-37200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-27200</v>
       </c>
       <c r="T33" s="3">
         <v>-27200</v>
       </c>
       <c r="U33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="V33" s="3">
         <v>-21700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-18800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-43100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-133200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-116000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-161500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-108400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-98300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-68100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-56500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-73300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-61200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-57600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-52700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-52900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-37200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-27200</v>
       </c>
       <c r="T35" s="3">
         <v>-27200</v>
       </c>
       <c r="U35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="V35" s="3">
         <v>-21700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-18800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-43100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,74 +3090,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>201300</v>
+      </c>
+      <c r="E41" s="3">
         <v>275700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>696100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>358400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>380300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>427200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>161400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>178900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>129200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>195600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>351600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>104300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>64900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>182700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21800</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,74 +3171,77 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1348200</v>
+      </c>
+      <c r="E42" s="3">
         <v>1315000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1415100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1156800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>454800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>529200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>482600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>483500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>476100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>355700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>421100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>468600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>479500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>450700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>330000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>336500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>401300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>301500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>165300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>106100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>114500</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,74 +3254,77 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,31 +3337,34 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3324,74 +3420,77 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>34000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>25700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>25100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>8200</v>
       </c>
       <c r="Q45" s="3">
         <v>8200</v>
       </c>
       <c r="R45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="S45" s="3">
         <v>7000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,74 +3503,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1579100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1624700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1729200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1879300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>824500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>922100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>922800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>660200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>675100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>483000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>534300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>589800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>623500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>661000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>697400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>454100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>482900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>340400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>362100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>134000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>149100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,31 +3586,34 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3564,74 +3669,77 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E48" s="3">
         <v>100600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>99900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>73300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>71200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,74 +3752,77 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E49" s="3">
         <v>71800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>75300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>75800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>76600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76900</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,74 +4001,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E52" s="3">
         <v>11300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1300</v>
       </c>
       <c r="P52" s="3">
         <v>1300</v>
       </c>
       <c r="Q52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="R52" s="3">
         <v>1400</v>
       </c>
       <c r="S52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,74 +4167,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1763000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1808400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1908400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2061700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>984200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1073700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1073200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>811900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>825900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>632800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>682800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>738000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>735000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>774000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>811700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>567400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>595100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>454000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>454300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>220500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>234700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,74 +4314,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E57" s="3">
         <v>29300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,31 +4395,34 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4311,17 +4445,17 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>100</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
       </c>
       <c r="U58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
@@ -4329,8 +4463,8 @@
       <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>200</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4344,74 +4478,77 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>76000</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
-        <v>61300</v>
+        <v>700</v>
       </c>
       <c r="F59" s="3">
-        <v>82100</v>
+        <v>700</v>
       </c>
       <c r="G59" s="3">
-        <v>55900</v>
+        <v>3900</v>
       </c>
       <c r="H59" s="3">
-        <v>48300</v>
+        <v>500</v>
       </c>
       <c r="I59" s="3">
-        <v>34700</v>
+        <v>400</v>
       </c>
       <c r="J59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K59" s="3">
         <v>40700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>43300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>46300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>35400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>33500</v>
       </c>
       <c r="U59" s="3">
         <v>33500</v>
       </c>
       <c r="V59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="W59" s="3">
         <v>31500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>32500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,74 +4561,77 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E60" s="3">
         <v>105300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>143900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>78100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>62000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>73300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>63500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>57500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>60400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>51900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>47200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>42400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>41500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,31 +4644,34 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>78300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>79100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>79900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>80600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>57100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>57500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>57700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4584,74 +4727,77 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>84300</v>
+        <v>4400</v>
       </c>
       <c r="E62" s="3">
-        <v>89200</v>
+        <v>2100</v>
       </c>
       <c r="F62" s="3">
-        <v>91700</v>
+        <v>6200</v>
       </c>
       <c r="G62" s="3">
-        <v>61200</v>
+        <v>8000</v>
       </c>
       <c r="H62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K62" s="3">
         <v>64800</v>
       </c>
-      <c r="I62" s="3">
-        <v>66400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>64800</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>71200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>70400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>74300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>75100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>43200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>49700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>27500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>30400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,74 +5059,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E66" s="3">
         <v>189600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>182900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>235500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>146800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>142900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>126700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>144500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>134000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>131800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>135400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>96800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>89000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>89100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>92700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>69000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>68000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5234,13 +5402,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>305100</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,74 +5505,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1543200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-976200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-867700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-769400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-701300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-644800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-571500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-510300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-452600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-400000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-347000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-302700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-265500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-231300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-204100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-176900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-157400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-142800</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,74 +5837,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1566300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1618800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1725500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1826200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>837500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>930800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>952200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>685200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>681400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>498800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>551000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>602600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>638200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>685000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>722600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>474700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>505100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>360500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>385300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-152600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-139400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-156300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-133200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-116000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-161500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-108400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-98300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-68100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-56500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-73300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-61200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-57600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-52700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-52900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-37200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-27200</v>
       </c>
       <c r="T81" s="3">
         <v>-27200</v>
       </c>
       <c r="U81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="V81" s="3">
         <v>-21700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-18800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-43100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,43 +6207,44 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E83" s="3">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="G83" s="3">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="H83" s="3">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1200</v>
       </c>
       <c r="M83" s="3">
         <v>1200</v>
       </c>
       <c r="N83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="O83" s="3">
         <v>1100</v>
@@ -6054,7 +6253,7 @@
         <v>1100</v>
       </c>
       <c r="Q83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>900</v>
@@ -6072,25 +6271,28 @@
         <v>900</v>
       </c>
       <c r="W83" s="3">
+        <v>900</v>
+      </c>
+      <c r="X83" s="3">
         <v>2500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-130400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-128200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-160600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-120600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-67100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-62400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-61800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-51700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-55700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-55200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-39300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-27000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-20000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-28000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-38000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13000</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,88 +6819,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E94" s="3">
         <v>107900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-248000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-380400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>77400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-123400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>62400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>44000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-122800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>62900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-101000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-136500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-59700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>8000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-110000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,31 +7182,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,111 +7512,117 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E100" s="3">
         <v>7500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>839400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>64600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>324200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>51400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>248300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>282300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>168900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>253700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>4200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>56600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7429,84 +7678,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-407700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>338400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-46000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>265800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>73200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-66400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-156000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>247300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>39400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>40900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-157800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>166000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-47800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>68300</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,128 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -790,104 +793,107 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9800</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>13400</v>
+        <v>188100</v>
       </c>
       <c r="E9" s="3">
+        <v>151800</v>
+      </c>
+      <c r="F9" s="3">
         <v>12800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>118000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>136600</v>
       </c>
-      <c r="H9" s="3">
-        <v>8200</v>
-      </c>
       <c r="I9" s="3">
+        <v>107700</v>
+      </c>
+      <c r="J9" s="3">
         <v>7600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>68900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -942,35 +948,38 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-13400</v>
+        <v>-188100</v>
       </c>
       <c r="E10" s="3">
+        <v>-151800</v>
+      </c>
+      <c r="F10" s="3">
         <v>-12800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-118000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-135800</v>
       </c>
-      <c r="H10" s="3">
-        <v>-8200</v>
-      </c>
       <c r="I10" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="J10" s="3">
         <v>-3800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-61900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1025,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>138400</v>
+        <v>188100</v>
       </c>
       <c r="E12" s="3">
+        <v>151800</v>
+      </c>
+      <c r="F12" s="3">
         <v>122200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>118000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>148500</v>
       </c>
-      <c r="H12" s="3">
-        <v>99600</v>
-      </c>
       <c r="I12" s="3">
+        <v>107700</v>
+      </c>
+      <c r="J12" s="3">
         <v>90300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>68900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>66100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>69500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>61000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>56500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>53700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>46500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>40900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>37000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32900</v>
-      </c>
-      <c r="V12" s="3">
-        <v>27500</v>
       </c>
       <c r="W12" s="3">
         <v>27500</v>
       </c>
       <c r="X12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="Y12" s="3">
         <v>64300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>18200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>32900</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1238,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1233,15 +1252,15 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>2800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1273,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1305,35 +1324,38 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1388,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>216300</v>
+      </c>
+      <c r="E17" s="3">
         <v>175700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>156600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>140900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>155200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>123200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>112600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>82200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>77000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>79900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>71200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>72500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>38500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-216300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-175700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-156600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-140900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-154500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-123200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-108800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-75200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-61700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-76500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-62100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-57900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-52900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-53200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-44500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-34000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-28000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-19600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,46 +1645,47 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>5100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
@@ -1661,126 +1694,132 @@
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-214800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-175100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-153000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-135400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-153100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-122000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-107500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-74000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-55200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-72400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-60000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-56500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-51600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-51900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-43200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-36200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-26300</v>
       </c>
       <c r="U21" s="3">
         <v>-26300</v>
       </c>
       <c r="V21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="W21" s="3">
         <v>-19300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-18100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1793,20 +1832,20 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1845,113 +1884,119 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-195300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-156300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-133200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-116000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-161200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-112300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-98300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-68100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-56600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-73600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-61200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-57600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-52700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-44300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-37200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-20200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-800</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1959,27 +2004,27 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3900</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1992,27 +2037,27 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4400</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,8 +2073,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-156300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-133200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-116000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-161500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-108400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-98300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-68100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-56500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-73300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-61200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-57600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-52700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-44300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-37200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-27200</v>
       </c>
       <c r="U26" s="3">
         <v>-27200</v>
       </c>
       <c r="V26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="W26" s="3">
         <v>-19500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-156300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-133200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-116000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-161500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-108400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-98300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-68100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-56500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-73300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-61200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-57600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-52700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-44300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-37200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-27200</v>
       </c>
       <c r="U27" s="3">
         <v>-27200</v>
       </c>
       <c r="V27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="W27" s="3">
         <v>-21700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,46 +2675,49 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
@@ -2657,126 +2726,132 @@
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1700</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-156300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-133200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-116000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-161500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-108400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-98300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-68100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-56500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-73300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-61200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-57600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-52700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-44300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-37200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-27200</v>
       </c>
       <c r="U33" s="3">
         <v>-27200</v>
       </c>
       <c r="V33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="W33" s="3">
         <v>-21700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-18800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-156300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-133200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-116000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-161500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-108400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-98300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-68100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-56500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-73300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-61200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-57600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-52700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-44300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-37200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-27200</v>
       </c>
       <c r="U35" s="3">
         <v>-27200</v>
       </c>
       <c r="V35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="W35" s="3">
         <v>-21700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-18800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,77 +3176,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>543100</v>
+      </c>
+      <c r="E41" s="3">
         <v>201300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>275700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>288400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>696100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>358400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>380300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>427200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>161400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>178900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>97700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>108500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>195600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>351600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>104300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>64900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>182700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,77 +3260,80 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1746200</v>
+      </c>
+      <c r="E42" s="3">
         <v>1348200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1315000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1415100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1156800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>454800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>529200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>482600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>483500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>476100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>355700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>421100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>468600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>479500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>450700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>330000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>336500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>401300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>301500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>165300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>106100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>114500</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3257,8 +3346,11 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3271,63 +3363,63 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3432,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3366,8 +3461,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3423,8 +3518,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3449,51 +3547,51 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>10600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>8200</v>
       </c>
       <c r="R45" s="3">
         <v>8200</v>
       </c>
       <c r="S45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="T45" s="3">
         <v>7000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3900</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,77 +3604,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2327600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1579100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1624700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1729200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1879300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>824500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>922100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>922800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>660200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>675100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>483000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>534300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>589800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>623500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>661000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>697400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>454100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>482900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>340400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>362100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>134000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>149100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,8 +3690,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3615,8 +3719,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3672,77 +3776,80 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>141800</v>
+      </c>
+      <c r="E48" s="3">
         <v>99200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>99900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>73700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>74500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>73300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>71600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>71200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,77 +3862,80 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E49" s="3">
         <v>71500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>74800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>75000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>75600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>75800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>76400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>76900</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,8 +3948,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,77 +4120,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E52" s="3">
         <v>13200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1300</v>
       </c>
       <c r="Q52" s="3">
         <v>1300</v>
       </c>
       <c r="R52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="S52" s="3">
         <v>1400</v>
       </c>
       <c r="T52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,77 +4292,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2558300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1763000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1808400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1908400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2061700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>984200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1073700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1073200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>811900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>825900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>632800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>682800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>738000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>735000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>774000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>811700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>567400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>595100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>454000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>454300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>220500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>234700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,77 +4444,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E57" s="3">
         <v>24500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>61800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,35 +4528,38 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E58" s="3">
         <v>8400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4448,17 +4581,17 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>100</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>200</v>
@@ -4466,8 +4599,8 @@
       <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>200</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
@@ -4481,77 +4614,80 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
       </c>
       <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>46300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>35400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>34600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>35700</v>
-      </c>
-      <c r="U59" s="3">
-        <v>33500</v>
       </c>
       <c r="V59" s="3">
         <v>33500</v>
       </c>
       <c r="W59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="X59" s="3">
         <v>31500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>32500</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,77 +4700,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E60" s="3">
         <v>110900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>105300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>143900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>78100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>54600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>62000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>57500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>60400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>45800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>42400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>41500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38600</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,35 +4786,38 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E61" s="3">
         <v>78300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>79100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>80600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>57100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4730,77 +4872,80 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E62" s="3">
         <v>4400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>71200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>70400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>74300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>75100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>45500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>47600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>49700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>27500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>30400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,77 +5216,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>293100</v>
+      </c>
+      <c r="E66" s="3">
         <v>196700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>189600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>235500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>146800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>142900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>121000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>126700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>134000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>131800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>135400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>96800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>89000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>89100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>92700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>69100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5405,13 +5572,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>305100</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5425,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,77 +5678,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1737800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-976200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-867700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-769400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-701300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-644800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-571500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-510300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-452600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-400000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-347000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-302700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-265500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-231300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-204100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-176900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-157400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-142800</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,77 +6022,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2265200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1566300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1618800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1725500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1826200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>837500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>930800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>952200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>685200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>681400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>498800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>551000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>602600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>638200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>685000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>722600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>474700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>505100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>360500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>385300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-152600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-139400</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-156300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-133200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-116000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-161500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-108400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-98300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-68100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-56500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-73300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-61200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-57600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-52700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-44300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-37200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-27200</v>
       </c>
       <c r="U81" s="3">
         <v>-27200</v>
       </c>
       <c r="V81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="W81" s="3">
         <v>-21700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-18800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,46 +6405,47 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2300</v>
       </c>
       <c r="G83" s="3">
         <v>2300</v>
       </c>
       <c r="H83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="I83" s="3">
         <v>2100</v>
       </c>
       <c r="J83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1200</v>
       </c>
       <c r="N83" s="3">
         <v>1200</v>
       </c>
       <c r="O83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="P83" s="3">
         <v>1100</v>
@@ -6256,7 +6454,7 @@
         <v>1100</v>
       </c>
       <c r="R83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>900</v>
@@ -6274,25 +6472,28 @@
         <v>900</v>
       </c>
       <c r="X83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-138300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-130400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-128200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-160600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-120600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-67100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-62400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-61800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-51700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-55700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-55200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-39300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-34100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-37200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-25000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-27000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-28000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13000</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,91 +7039,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-392900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>107900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-248000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-380400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>77400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-123400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>62400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>44000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>8500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-122800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>62900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-101000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-136500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-59700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>8000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-110000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7209,8 +7442,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7266,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,91 +7757,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>873800</v>
+      </c>
+      <c r="E100" s="3">
         <v>77300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>839400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>64600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>324200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>51400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>248300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>282300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>168900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>253700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>4200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>56600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7624,8 +7872,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7681,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>342600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-407700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>338400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-46000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>265800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>73200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-66400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-156000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>247300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>40900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-157800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>166000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-47800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>68300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,131 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -796,107 +800,110 @@
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>38000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9800</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>205700</v>
+      </c>
+      <c r="E9" s="3">
         <v>188100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>151800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>118000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>136600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>107700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>68900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,38 +958,41 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-205700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-188100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-151800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-12800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-118000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-135800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-107700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-3800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-61900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>205700</v>
+      </c>
+      <c r="E12" s="3">
         <v>188100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>151800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>122200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>118000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>148500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>107700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>90300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>68900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>66100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>69500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>61000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>56500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>53700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>46500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>40900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>37000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>34900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>32900</v>
-      </c>
-      <c r="W12" s="3">
-        <v>27500</v>
       </c>
       <c r="X12" s="3">
         <v>27500</v>
       </c>
       <c r="Y12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="Z12" s="3">
         <v>64300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>18200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>32900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,8 +1258,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1255,15 +1275,15 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>25500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1276,8 +1296,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1327,8 +1347,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,29 +1359,29 @@
         <v>1700</v>
       </c>
       <c r="E15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>240800</v>
+      </c>
+      <c r="E17" s="3">
         <v>216300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>175700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>140900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>155200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>123200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>112600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>82200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>77000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>79900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>71200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>38000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>32600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>72500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>38500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-240800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-216300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-175700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-156600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-140900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-154500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-123200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-108800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-75200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-61700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-76500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-62100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-57900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-53200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-44500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-34000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-27500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-28000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,49 +1679,50 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
@@ -1697,129 +1731,135 @@
         <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>200</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-236700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-214800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-175100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-153000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-135400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-138300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-153100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-122000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-107500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-74000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-55200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-72400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-60000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-56500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-51600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-51900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-43200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-36200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-26300</v>
       </c>
       <c r="V21" s="3">
         <v>-26300</v>
       </c>
       <c r="W21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="X21" s="3">
         <v>-19300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1835,20 +1875,20 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1887,147 +1927,153 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-195300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-156300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-133200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-116000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-161200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-112300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-98300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-68100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-56600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-61200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-57600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-44300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-37200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3900</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2040,27 +2086,27 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,8 +2122,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-194600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-156300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-133200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-116000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-161500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-108400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-68100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-56500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-73300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-61200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-57600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-52900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-44300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-37200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-27200</v>
       </c>
       <c r="V26" s="3">
         <v>-27200</v>
       </c>
       <c r="W26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="X26" s="3">
         <v>-19500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-194600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-156300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-133200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-116000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-161500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-108400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-98300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-68100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-73300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-61200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-57600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-52900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-44300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-37200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-27200</v>
       </c>
       <c r="V27" s="3">
         <v>-27200</v>
       </c>
       <c r="W27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="X27" s="3">
         <v>-21700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-43100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,49 +2745,52 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="G32" s="3">
-        <v>3900</v>
-      </c>
       <c r="H32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
@@ -2729,129 +2799,135 @@
         <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1700</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-194600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-156300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-133200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-116000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-161500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-108400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-98300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-68100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-73300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-61200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-57600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-52900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-44300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-37200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-27200</v>
       </c>
       <c r="V33" s="3">
         <v>-27200</v>
       </c>
       <c r="W33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="X33" s="3">
         <v>-21700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-43100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-194600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-156300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-133200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-116000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-161500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-108400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-98300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-68100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-73300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-61200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-57600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-52900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-44300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-37200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-27200</v>
       </c>
       <c r="V35" s="3">
         <v>-27200</v>
       </c>
       <c r="W35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="X35" s="3">
         <v>-21700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-43100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,80 +3263,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>333600</v>
+      </c>
+      <c r="E41" s="3">
         <v>543100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>201300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>275700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>288400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>696100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>358400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>380300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>427200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>161400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>178900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>105800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>97700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>108500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>129200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>195600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>351600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>104300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>64900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>182700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,80 +3350,83 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1769100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1746200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1348200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1315000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1415100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1156800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>454800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>529200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>482600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>483500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>476100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>355700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>421100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>468600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>479500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>450700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>330000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>336500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>401300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>301500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>165300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>106100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>114500</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3439,11 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3366,63 +3459,63 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3464,8 +3560,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3521,8 +3617,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3550,51 +3649,51 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>8200</v>
       </c>
       <c r="S45" s="3">
         <v>8200</v>
       </c>
       <c r="T45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="U45" s="3">
         <v>7000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3900</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,80 +3706,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2134600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2327600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1579100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1624700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1729200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1879300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>824500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>922100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>922800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>660200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>675100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>483000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>534300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>589800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>623500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>661000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>697400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>454100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>482900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>340400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>362100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>134000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>149100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,8 +3795,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3722,8 +3827,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3779,80 +3884,83 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E48" s="3">
         <v>141800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>99200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>99900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>73700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>74500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>73300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>71600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>71200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>37600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,80 +3973,83 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E49" s="3">
         <v>71300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>74500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>74800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>75300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>75600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>75800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>76100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>76600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>76900</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,80 +4240,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E52" s="3">
         <v>17600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1300</v>
       </c>
       <c r="R52" s="3">
         <v>1300</v>
       </c>
       <c r="S52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="T52" s="3">
         <v>1400</v>
       </c>
       <c r="U52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,80 +4418,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2365400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2558300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1763000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1808400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1908400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2061700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>984200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1073700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1073200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>811900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>825900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>632800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>682800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>738000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>735000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>774000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>811700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>567400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>595100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>454000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>454300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>220500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>234700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,80 +4575,81 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E57" s="3">
         <v>54400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>61800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,38 +4662,41 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4584,17 +4718,17 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
-        <v>100</v>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>100</v>
       </c>
       <c r="W58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X58" s="3">
         <v>200</v>
@@ -4602,8 +4736,8 @@
       <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
+      <c r="Z58" s="3">
+        <v>200</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
@@ -4617,80 +4751,83 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>700</v>
       </c>
       <c r="G59" s="3">
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>40700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>49500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>35400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>34100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>33500</v>
       </c>
       <c r="W59" s="3">
         <v>33500</v>
       </c>
       <c r="X59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="Y59" s="3">
         <v>31500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>32500</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,80 +4840,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E60" s="3">
         <v>163900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>110900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>105300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>143900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>78100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>54600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>62000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>73300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>63500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>57500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>45800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>41500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38600</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,38 +4929,41 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>121400</v>
+      </c>
+      <c r="E61" s="3">
         <v>123000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>78300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>80600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4875,80 +5018,83 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>64800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>71200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>70400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>74300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>75100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>45300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>47600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>49700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>27500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,80 +5374,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>287200</v>
+      </c>
+      <c r="E66" s="3">
         <v>293100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>196700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>189600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>235500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>146800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>142900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>121000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>126700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>144500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>134000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>131800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>135400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>96800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>89000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>89100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>92700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>90000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>93500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>68000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>69100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5575,13 +5743,13 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>305100</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,80 +5852,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1951200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1737800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-976200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-867700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-769400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-701300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-644800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-571500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-510300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-452600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-400000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-347000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-302700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-265500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-231300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-204100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-176900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-157400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-142800</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,80 +6208,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2078200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2265200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1566300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1618800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1725500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1826200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>837500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>930800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>952200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>685200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>681400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>498800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>551000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>602600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>638200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>685000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>722600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>474700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>505100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>360500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>385300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-152600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-139400</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-213400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-194600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-156300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-133200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-116000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-161500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-108400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-98300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-68100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-73300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-61200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-57600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-52900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-44300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-37200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-27200</v>
       </c>
       <c r="V81" s="3">
         <v>-27200</v>
       </c>
       <c r="W81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="X81" s="3">
         <v>-21700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-43100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,49 +6604,50 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2300</v>
       </c>
       <c r="H83" s="3">
         <v>2300</v>
       </c>
       <c r="I83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="J83" s="3">
         <v>2100</v>
       </c>
       <c r="K83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1200</v>
       </c>
       <c r="O83" s="3">
         <v>1200</v>
       </c>
       <c r="P83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="Q83" s="3">
         <v>1100</v>
@@ -6457,7 +6656,7 @@
         <v>1100</v>
       </c>
       <c r="S83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="T83" s="3">
         <v>900</v>
@@ -6475,25 +6674,28 @@
         <v>900</v>
       </c>
       <c r="Y83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-194400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-138300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-130400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-128200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-160600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-120600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-67100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-62400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-61800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-51700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-55700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-55200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-36600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-34100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-37200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-25000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-27000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-28000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13000</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,94 +7260,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-392900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>107900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-248000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-380400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>77400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-43500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-123400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>62400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>44000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>8500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-122800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>62900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-101000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-136500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-59700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>8000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-110000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7445,8 +7679,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,94 +8003,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>873800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>77300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>839400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>64600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>324200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>51400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>248300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>282300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>168900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>253700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>4200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>56600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7875,8 +8124,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-209500</v>
+      </c>
+      <c r="E102" s="3">
         <v>342600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-74600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-407700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>338400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-46000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>265800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>73200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-66400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-156000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>247300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>40900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-157800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>166000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-47800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>68300</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,135 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,110 +807,113 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>38000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9800</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E9" s="3">
         <v>205700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>188100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>151800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>118000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>136600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>107700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>68900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,41 +968,44 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-205700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-188100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-151800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-12800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-118000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-135800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-107700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-3800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-61900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1096,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E12" s="3">
         <v>205700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>188100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>151800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>122200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>118000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>148500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>107700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>90300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>68900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>66100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>69500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>61000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>56500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>53700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>46500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>45900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>40900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>37000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>32900</v>
-      </c>
-      <c r="X12" s="3">
-        <v>27500</v>
       </c>
       <c r="Y12" s="3">
         <v>27500</v>
       </c>
       <c r="Z12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="AA12" s="3">
         <v>64300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>21200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>18200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>32900</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1278,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1281,12 +1301,12 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>25500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,8 +1319,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1350,41 +1370,44 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="3">
         <v>1700</v>
       </c>
       <c r="F15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G15" s="3">
         <v>1600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1439,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>264700</v>
+      </c>
+      <c r="E17" s="3">
         <v>240800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>216300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>175700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>156600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>140900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>155200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>123200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>112600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>82200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>77000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>79900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>71200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>65500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>42800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>38000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>32600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>72500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>23600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>38500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-264700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-240800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-216300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-175700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-156600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-140900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-154500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-123200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-108800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-75200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-61700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-76500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-62100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-52900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-53200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-44500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-37400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-34000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-27500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-28000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-34500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,52 +1713,53 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>200</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
@@ -1734,132 +1768,138 @@
         <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-268400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-236700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-214800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-175100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-153000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-138300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-153100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-122000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-107500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-74000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-55200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-72400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-60000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-51600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-51900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-43200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-36200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-26300</v>
       </c>
       <c r="W21" s="3">
         <v>-26300</v>
       </c>
       <c r="X21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-18100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1878,20 +1918,20 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1930,153 +1970,159 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-213400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-195300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-156300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-133200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-116000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-161200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-112300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-98300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-68100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-56600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-73600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-61200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-52900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-37200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-33100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3900</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2089,27 +2135,27 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,8 +2171,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2263,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-213400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-194600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-156300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-133200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-116000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-161500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-108400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-68100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-56500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-73300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-61200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-52700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-52900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-37200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-27200</v>
       </c>
       <c r="W26" s="3">
         <v>-27200</v>
       </c>
       <c r="X26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-33100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-213400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-194600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-156300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-133200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-116000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-161500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-108400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-98300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-68100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-56500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-73300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-61200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-52700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-52900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-37200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-27200</v>
       </c>
       <c r="W27" s="3">
         <v>-27200</v>
       </c>
       <c r="X27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-43100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,52 +2815,55 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-200</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
@@ -2802,132 +2872,138 @@
         <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1700</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-213400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-194600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-156300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-133200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-116000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-161500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-108400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-98300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-68100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-56500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-73300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-61200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-52700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-52900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-37200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-27200</v>
       </c>
       <c r="W33" s="3">
         <v>-27200</v>
       </c>
       <c r="X33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-43100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-213400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-194600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-156300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-133200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-116000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-161500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-108400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-98300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-68100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-56500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-73300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-61200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-52700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-52900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-37200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-27200</v>
       </c>
       <c r="W35" s="3">
         <v>-27200</v>
       </c>
       <c r="X35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-43100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,83 +3350,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>402400</v>
+      </c>
+      <c r="E41" s="3">
         <v>333600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>543100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>201300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>275700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>288400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>696100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>358400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>380300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>427200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>161400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>178900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>108500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>129200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>195600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>351600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>104300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>64900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>182700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21800</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,83 +3440,86 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1734700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1769100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1746200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1348200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1315000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1415100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1156800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>454800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>529200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>482600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>483500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>476100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>355700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>421100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>468600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>479500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>450700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>330000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>336500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>401300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>301500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>165300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>106100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>114500</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,8 +3532,11 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3462,63 +3555,63 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3624,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3563,8 +3659,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3620,8 +3716,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3652,51 +3751,51 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>10600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>8200</v>
       </c>
       <c r="T45" s="3">
         <v>8200</v>
       </c>
       <c r="U45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="V45" s="3">
         <v>7000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3900</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,83 +3808,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2176400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2134600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2327600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1579100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1624700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1729200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1879300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>824500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>922100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>922800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>660200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>675100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>483000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>534300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>589800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>623500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>661000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>697400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>454100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>482900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>340400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>362100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>134000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>149100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +3900,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3830,8 +3935,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3887,83 +3992,86 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E48" s="3">
         <v>142900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>141800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>99200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>99900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>73500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>73700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>74500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>73300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>71600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>71200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>37600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>36000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3976,83 +4084,86 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E49" s="3">
         <v>71000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>73700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>74200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>74500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>74800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>75000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>75300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>75600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>76400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>76600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>76900</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4065,8 +4176,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,83 +4360,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E52" s="3">
         <v>16800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1300</v>
       </c>
       <c r="S52" s="3">
         <v>1300</v>
       </c>
       <c r="T52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="U52" s="3">
         <v>1400</v>
       </c>
       <c r="V52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,83 +4544,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2429600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2365400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2558300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1763000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1808400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1908400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2061700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>984200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1073700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1073200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>811900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>825900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>632800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>682800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>738000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>735000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>774000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>811700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>567400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>595100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>454000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>454300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>220500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>234700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,83 +4706,84 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E57" s="3">
         <v>47500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>61800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>21300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,41 +4796,44 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E58" s="3">
         <v>13000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4721,17 +4855,17 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
-        <v>100</v>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>100</v>
       </c>
       <c r="X58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
         <v>200</v>
@@ -4739,8 +4873,8 @@
       <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
+      <c r="AA58" s="3">
+        <v>200</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
@@ -4754,83 +4888,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>700</v>
       </c>
       <c r="H59" s="3">
         <v>700</v>
       </c>
       <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>35700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>33500</v>
       </c>
       <c r="X59" s="3">
         <v>33500</v>
       </c>
       <c r="Y59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>31500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>32500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,83 +4980,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>184500</v>
+      </c>
+      <c r="E60" s="3">
         <v>158600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>163900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>105300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>143900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>54600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>62000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>73300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>63500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>57500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>60400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>45800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>42400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>41500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38600</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,41 +5072,44 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E61" s="3">
         <v>121400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>78300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>80600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5021,83 +5164,86 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>257600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>64800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>71200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>70400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>74300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>75100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>44900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>47600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>49700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>30400</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5256,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,83 +5532,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>564200</v>
+      </c>
+      <c r="E66" s="3">
         <v>287200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>293100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>196700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>189600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>235500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>146800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>142900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>121000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>126700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>144500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>134000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>131800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>135400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>96800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>89000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>89100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>92700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>90000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>93500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>69000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>68000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>69100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5746,13 +5914,13 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>305100</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -5766,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,83 +6026,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2199000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1951200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1737800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-976200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-867700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-769400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-701300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-644800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-571500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-510300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-452600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-400000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-347000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-302700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-265500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-231300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-204100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-176900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-157400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-142800</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,83 +6394,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1865400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2078200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2265200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1566300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1618800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1725500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1826200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>837500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>930800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>952200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>685200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>681400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>498800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>551000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>602600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>638200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>685000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>722600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>474700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>505100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>360500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>385300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-152600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-139400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-247800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-213400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-194600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-156300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-133200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-116000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-161500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-108400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-98300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-68100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-56500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-73300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-61200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-52700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-52900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-37200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-27200</v>
       </c>
       <c r="W81" s="3">
         <v>-27200</v>
       </c>
       <c r="X81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-43100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6614,43 +6813,43 @@
         <v>2500</v>
       </c>
       <c r="E83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F83" s="3">
         <v>2600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2300</v>
       </c>
       <c r="I83" s="3">
         <v>2300</v>
       </c>
       <c r="J83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="K83" s="3">
         <v>2100</v>
       </c>
       <c r="L83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1200</v>
       </c>
       <c r="P83" s="3">
         <v>1200</v>
       </c>
       <c r="Q83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
@@ -6659,7 +6858,7 @@
         <v>1100</v>
       </c>
       <c r="T83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>900</v>
@@ -6677,25 +6876,28 @@
         <v>900</v>
       </c>
       <c r="Z83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1100</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7353,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-221800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-194400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-138300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-130400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-128200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-160600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-120600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-67100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-62400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-61800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-51700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-55700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-55200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-39300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-36600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-34100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-37200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-25000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-27000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,97 +7481,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,97 +7755,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-392900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>107900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-248000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-380400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>77400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-123400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>62400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>44000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>8500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-122800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>62900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-101000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-136500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-59700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>8000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-110000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7682,8 +7916,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7739,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,97 +8249,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>256600</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>873800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>77300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>839400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>64600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>324200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>51400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>248300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>282300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>168900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>253700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>4200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>56600</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8127,8 +8376,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8184,93 +8433,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-209500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>342600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-74600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-407700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>338400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-46000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>265800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-66400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-156000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>247300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>39400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>40900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-157800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>166000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-47800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>68300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,143 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -817,116 +820,119 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>3800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>38000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9800</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>294900</v>
+      </c>
+      <c r="E9" s="3">
         <v>262500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>205700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>188100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>136600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>107700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>68900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,47 +987,50 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-294900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-262500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-19100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-205700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-188100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-151800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-12800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-118000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-135800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-107700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-3800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-61900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>294900</v>
+      </c>
+      <c r="E12" s="3">
         <v>262500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>205000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>205700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>188100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>151800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>122200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>118000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>148500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>90300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>68900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>66100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>69500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>61000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>56500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>53700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>46500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>45900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>40900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>37000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>34900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>32900</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>27500</v>
       </c>
       <c r="AA12" s="3">
         <v>27500</v>
       </c>
       <c r="AB12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="AC12" s="3">
         <v>64300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>21200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>18200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>32900</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1317,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1327,12 +1346,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>25500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1345,8 +1364,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1396,47 +1415,50 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1700</v>
       </c>
       <c r="G15" s="3">
         <v>1700</v>
       </c>
       <c r="H15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1491,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E17" s="3">
         <v>315300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>264700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>240800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>216300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>175700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>156600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>155200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>123200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>112600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>82200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>77000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>79900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>71200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>65500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>62400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>32600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>72500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>38500</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-361600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-315300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-264700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-240800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-216300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-175700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-156600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-140900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-154500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-123200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-108800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-75200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-61700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-76500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-62100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-57900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-52900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-53200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-44500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-37400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-34000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-27500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-21100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,58 +1780,59 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>5100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
@@ -1808,147 +1841,153 @@
         <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>200</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-372000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-313800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-268400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-236700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-214800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-175100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-153000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-138300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-153100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-122000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-107500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-74000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-55200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-72400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-60000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-56500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-51600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-51900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-43200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-36200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-26300</v>
       </c>
       <c r="Y21" s="3">
         <v>-26300</v>
       </c>
       <c r="Z21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E22" s="3">
         <v>11400</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,20 +2003,20 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2016,120 +2055,126 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-305200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-247800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-213400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-195300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-156300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-133200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-116000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-161200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-112300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-98300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-68100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-56600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-73600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-61200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-57600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-52700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-52900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-44300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-37200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-33800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-33100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2142,39 +2187,39 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2187,27 +2232,27 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2223,8 +2268,11 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-305200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-247800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-213400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-194600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-156300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-133200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-116000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-161500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-108400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-98300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-68100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-56500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-61200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-57600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-52700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-52900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-44300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-37200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-27200</v>
       </c>
       <c r="Y26" s="3">
         <v>-27200</v>
       </c>
       <c r="Z26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-19500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-33100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-305200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-247800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-213400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-194600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-156300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-133200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-116000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-161500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-108400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-98300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-68100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-61200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-57600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-52700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-52900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-44300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-37200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-27200</v>
       </c>
       <c r="Y27" s="3">
         <v>-27200</v>
       </c>
       <c r="Z27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-21700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-43100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,58 +2954,61 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-5100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
@@ -2948,138 +3017,144 @@
         <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1700</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-305200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-247800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-213400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-194600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-156300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-133200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-116000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-161500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-108400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-98300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-68100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-61200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-57600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-52700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-52900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-44300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-37200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-27200</v>
       </c>
       <c r="Y33" s="3">
         <v>-27200</v>
       </c>
       <c r="Z33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-21700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-43100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-305200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-247800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-213400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-194600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-156300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-133200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-116000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-161500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-108400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-98300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-68100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-61200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-57600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-52700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-52900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-44300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-37200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-27200</v>
       </c>
       <c r="Y35" s="3">
         <v>-27200</v>
       </c>
       <c r="Z35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-21700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-43100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,89 +3523,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>383700</v>
+      </c>
+      <c r="E41" s="3">
         <v>217400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>402400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>333600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>543100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>201300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>275700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>288400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>696100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>358400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>380300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>427200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>161400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>178900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>105800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>97700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>108500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>129200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>195600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>351600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>104300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>182700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21800</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,89 +3619,92 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1641900</v>
+      </c>
+      <c r="E42" s="3">
         <v>1714100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1734700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1769100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1746200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1348200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1315000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1415100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1156800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>454800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>529200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>482600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>483500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>476100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>355700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>421100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>468600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>479500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>450700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>330000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>336500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>401300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>301500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>165300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>106100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>114500</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3717,11 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3654,63 +3746,63 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>9000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,8 +3815,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3761,8 +3856,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3818,8 +3913,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3856,51 +3954,51 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>10600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>8200</v>
       </c>
       <c r="V45" s="3">
         <v>8200</v>
       </c>
       <c r="W45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="X45" s="3">
         <v>7000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3900</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,89 +4011,92 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2075000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1977500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2176400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2134600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2327600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1579100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1624700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1729200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1879300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>824500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>922100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>922800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>660200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>675100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>483000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>534300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>589800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>623500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>661000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>697400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>454100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>482900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>340400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>362100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>134000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>149100</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4008,8 +4109,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4046,8 +4150,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4103,89 +4207,92 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E48" s="3">
         <v>167400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>147000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>142900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>141800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>99200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>99900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>73400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>73500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>73700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>74500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>73300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>71600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>71200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>37600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>36300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>36000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>15200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,89 +4305,92 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E49" s="3">
         <v>70500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>70700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>72600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>72900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>73100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>73400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>73700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>74000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>74200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>74500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>74800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>75000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>75600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>75800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>76100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>76400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>76600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>76900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4293,8 +4403,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,89 +4599,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>19700</v>
+        <v>43800</v>
       </c>
       <c r="E52" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F52" s="3">
         <v>35300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1300</v>
       </c>
       <c r="U52" s="3">
         <v>1300</v>
       </c>
       <c r="V52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="W52" s="3">
         <v>1400</v>
       </c>
       <c r="X52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4578,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,89 +4795,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2354500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2251900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2429600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2365400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2558300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1763000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1808400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1908400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2061700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>984200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1073700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1073200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>811900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>825900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>632800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>682800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>738000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>735000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>774000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>811700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>567400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>595100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>454000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>454300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>220500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>234700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4768,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,89 +4967,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E57" s="3">
         <v>74800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6000</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,47 +5063,50 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E58" s="3">
         <v>16300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4995,17 +5128,17 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3">
-        <v>100</v>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>100</v>
       </c>
       <c r="Z58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA58" s="3">
         <v>200</v>
@@ -5013,8 +5146,8 @@
       <c r="AB58" s="3">
         <v>200</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
+      <c r="AC58" s="3">
+        <v>200</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
@@ -5028,89 +5161,92 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>700</v>
       </c>
       <c r="J59" s="3">
         <v>700</v>
       </c>
       <c r="K59" s="3">
+        <v>700</v>
+      </c>
+      <c r="L59" s="3">
         <v>3900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>43300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>46300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>41400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>34100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35700</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>33500</v>
       </c>
       <c r="Z59" s="3">
         <v>33500</v>
       </c>
       <c r="AA59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="AB59" s="3">
         <v>31500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>32500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5123,89 +5259,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>290400</v>
+      </c>
+      <c r="E60" s="3">
         <v>245600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>184500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>158600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>163900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>110900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>143900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>62000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>73300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>63500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>57500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>60400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>45800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>47200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>42400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>38600</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5218,47 +5357,50 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>142100</v>
+        <v>410700</v>
       </c>
       <c r="E61" s="3">
+        <v>398600</v>
+      </c>
+      <c r="F61" s="3">
         <v>119700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>121400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>123000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>78300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>79100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>80600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5313,89 +5455,92 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>264900</v>
+        <v>19800</v>
       </c>
       <c r="E62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F62" s="3">
         <v>257600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>64800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>71200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>70400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>74300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>75100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>44900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>45300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>47600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>49700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5408,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,89 +5847,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>723200</v>
+      </c>
+      <c r="E66" s="3">
         <v>655000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>564200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>287200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>293100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>196700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>189600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>182900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>235500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>146800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>142900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>121000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>126700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>144500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>134000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>131800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>135400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>96800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>89000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>89100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>92700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>90000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>93500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>69000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>68000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>69100</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6088,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>305100</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
@@ -6108,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,89 +6373,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2869100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2504200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2199000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1951200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1737800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-976200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-867700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-769400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-701300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-644800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-571500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-510300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-452600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-400000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-347000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-302700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-265500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-231300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-204100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-176900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-142800</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,89 +6765,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1631300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1596900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1865400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2078200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2265200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1566300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1618800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1725500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1826200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>837500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>930800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>952200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>685200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>681400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>498800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>551000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>602600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>638200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>685000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>722600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>474700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>505100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>360500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>385300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-152600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-139400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-305200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-247800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-213400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-194600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-156300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-133200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-116000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-161500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-108400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-98300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-68100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-61200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-57600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-52700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-52900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-44300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-37200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-27200</v>
       </c>
       <c r="Y81" s="3">
         <v>-27200</v>
       </c>
       <c r="Z81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-21700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-43100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,58 +7200,59 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2500</v>
       </c>
       <c r="F83" s="3">
         <v>2500</v>
       </c>
       <c r="G83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2300</v>
       </c>
       <c r="K83" s="3">
         <v>2300</v>
       </c>
       <c r="L83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="M83" s="3">
         <v>2100</v>
       </c>
       <c r="N83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1200</v>
       </c>
       <c r="R83" s="3">
         <v>1200</v>
       </c>
       <c r="S83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
@@ -7063,7 +7261,7 @@
         <v>1100</v>
       </c>
       <c r="V83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="W83" s="3">
         <v>900</v>
@@ -7081,25 +7279,28 @@
         <v>900</v>
       </c>
       <c r="AB83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1100</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-274200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-207300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-221800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-194400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-138300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-130400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-128200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-160600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-120600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-67100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-61800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-51700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-55700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-55200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-39300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-36600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-34100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-37200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-25000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-12600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>13000</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7922,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E94" s="3">
         <v>24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>34300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-392900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>107900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-248000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-380400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>77400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>62400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>44000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>8500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-30200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-122800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>62900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-101000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-136500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-110000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8156,8 +8389,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8213,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8740,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>365700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>256600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>873800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>77300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>839400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>64600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>324200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>51400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>248300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>282300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>168900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>253700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100200</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>4200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>56600</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8631,8 +8879,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8688,99 +8936,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-184100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>69100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-209500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>342600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-74600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-407700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>338400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-46000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>265800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>73200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-66400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-156000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>247300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>39400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>40900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-157800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>166000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-47800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>68300</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>RVMD</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -823,119 +827,122 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
         <v>3800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>38000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9800</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E9" s="3">
         <v>294900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>262500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>205700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>188100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>151800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>136600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>107700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68900</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -990,50 +997,53 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-344000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-294900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-262500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-19100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-205700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-188100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-151800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-12800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-118000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-135800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-107700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-61900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1098,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,106 +1137,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E12" s="3">
         <v>294900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>262500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>205000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>205700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>188100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>151800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>122200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>118000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>148500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>90300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>68900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>66100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>69500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>61000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>56500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>53700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>46500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>45900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>40900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>37000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>34900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>32900</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>27500</v>
       </c>
       <c r="AB12" s="3">
         <v>27500</v>
       </c>
       <c r="AC12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="AD12" s="3">
         <v>64300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>21200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>18200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>32900</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,8 +1337,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,12 +1369,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>25500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1367,8 +1387,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1418,50 +1438,53 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1700</v>
       </c>
       <c r="H15" s="3">
         <v>1700</v>
       </c>
       <c r="I15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1516,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>445200</v>
+      </c>
+      <c r="E17" s="3">
         <v>361600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>315300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>264700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>240800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>216300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>175700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>140900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>123200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>112600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>82200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>77000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>79900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>71200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>65500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>62400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>54300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>42800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>40200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>38000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>32600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>72500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>23600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>38500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-445200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-361600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-315300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-264700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-240800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-216300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-175700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-156600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-140900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-154500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-123200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-108800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-75200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-76500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-62100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-57900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-52900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-53200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-44500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-37400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-21100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-34500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-28700</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,61 +1814,62 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E20" s="3">
         <v>12600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
@@ -1844,153 +1878,159 @@
         <v>200</v>
       </c>
       <c r="W20" s="3">
+        <v>200</v>
+      </c>
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-458800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-372000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-313800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-268400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-236700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-214800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-175100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-153000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-138300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-153100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-122000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-107500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-74000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-55200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-72400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-60000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-56500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-51600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-51900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-43200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-36200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-32900</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-26300</v>
       </c>
       <c r="Z21" s="3">
         <v>-26300</v>
       </c>
       <c r="AA21" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-19300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-18100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-30500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-29300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E22" s="3">
         <v>11900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11400</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,20 +2046,20 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2058,123 +2098,129 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-364900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-305200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-247800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-213400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-195300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-156300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-133200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-116000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-161200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-112300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-98300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-68100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-73600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-61200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-57600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-52700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-52900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-44300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-37200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-33800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-20200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-33100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2190,39 +2236,39 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2235,27 +2281,27 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2271,8 +2317,11 @@
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-364900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-305200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-247800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-213400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-194600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-156300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-133200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-116000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-161500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-108400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-68100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-73300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-61200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-57600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-52700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-52900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-44300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-37200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-27200</v>
       </c>
       <c r="Z26" s="3">
         <v>-27200</v>
       </c>
       <c r="AA26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-19500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-33100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-364900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-305200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-247800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-213400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-194600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-156300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-133200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-116000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-161500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-108400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-98300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-68100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-73300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-61200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-57600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-52700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-52900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-44300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-37200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-27200</v>
       </c>
       <c r="Z27" s="3">
         <v>-27200</v>
       </c>
       <c r="AA27" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-43100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,61 +3024,64 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
@@ -3020,141 +3090,147 @@
         <v>-200</v>
       </c>
       <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1700</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-364900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-305200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-247800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-213400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-194600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-156300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-133200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-116000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-161500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-108400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-98300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-68100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-73300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-61200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-57600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-52700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-52900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-44300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-37200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-27200</v>
       </c>
       <c r="Z33" s="3">
         <v>-27200</v>
       </c>
       <c r="AA33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-43100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-364900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-305200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-247800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-213400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-194600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-156300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-133200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-116000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-161500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-108400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-98300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-68100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-73300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-61200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-57600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-52700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-52900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-44300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-37200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-27200</v>
       </c>
       <c r="Z35" s="3">
         <v>-27200</v>
       </c>
       <c r="AA35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-43100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,92 +3610,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>440900</v>
+      </c>
+      <c r="E41" s="3">
         <v>383700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>217400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>402400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>333600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>543100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>201300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>275700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>288400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>696100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>358400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>380300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>427200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>161400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>178900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>105800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>97700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>129200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>195600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>351600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>104300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>64900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>182700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21800</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,92 +3709,95 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1467100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1641900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1714100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1734700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1769100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1746200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1348200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1315000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1415100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1156800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>454800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>529200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>482600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>483500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>476100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>355700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>421100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>468600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>479500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>450700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>330000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>336500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>401300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>301500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>165300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>106100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>114500</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3810,11 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3749,63 +3842,63 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>9000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3818,8 +3911,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3859,8 +3955,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3916,8 +4012,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3957,51 +4056,51 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>10600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>8200</v>
       </c>
       <c r="W45" s="3">
         <v>8200</v>
       </c>
       <c r="X45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Y45" s="3">
         <v>7000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3900</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4014,92 +4113,95 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1967900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2075000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1977500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2176400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2134600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2327600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1579100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1624700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1729200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1879300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>824500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>922100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>922800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>660200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>675100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>483000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>534300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>589800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>623500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>661000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>697400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>454100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>482900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>340400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>362100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>134000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>149100</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4112,8 +4214,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4153,8 +4258,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4210,92 +4315,95 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E48" s="3">
         <v>165300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>167400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>147000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>142900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>141800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>99200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>73400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>73500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>73700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>74500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>73300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>71600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>71200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>37600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>36300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>36000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4308,8 +4416,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4317,83 +4428,83 @@
         <v>70400</v>
       </c>
       <c r="E49" s="3">
+        <v>70400</v>
+      </c>
+      <c r="F49" s="3">
         <v>70500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>72300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>72600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>72900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>73100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>73400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>73700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>74000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>74200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>74500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>74800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>75300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>75600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>75800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>76100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>76400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>76600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>76900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4406,8 +4517,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,92 +4719,95 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E52" s="3">
         <v>43800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1300</v>
       </c>
       <c r="V52" s="3">
         <v>1300</v>
       </c>
       <c r="W52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="X52" s="3">
         <v>1400</v>
       </c>
       <c r="Y52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4700,8 +4820,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,92 +4921,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2253700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2354500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2251900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2429600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2365400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2558300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1763000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1808400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1908400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2061700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>984200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1073700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1073200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>811900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>825900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>632800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>682800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>738000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>735000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>774000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>811700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>567400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>595100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>454000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>454300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>220500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>234700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4896,8 +5022,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,92 +5098,93 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E57" s="3">
         <v>64600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>21300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5066,50 +5197,53 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E58" s="3">
         <v>16500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5131,17 +5265,17 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>100</v>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>100</v>
       </c>
       <c r="AA58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB58" s="3">
         <v>200</v>
@@ -5149,8 +5283,8 @@
       <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
+      <c r="AD58" s="3">
+        <v>200</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
@@ -5164,92 +5298,95 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>700</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
       </c>
       <c r="L59" s="3">
+        <v>700</v>
+      </c>
+      <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>43300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>41400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>35400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35700</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>33500</v>
       </c>
       <c r="AA59" s="3">
         <v>33500</v>
       </c>
       <c r="AB59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="AC59" s="3">
         <v>31500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>32500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5262,92 +5399,95 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>289600</v>
+      </c>
+      <c r="E60" s="3">
         <v>290400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>245600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>184500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>158600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>163900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>110900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>105300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>143900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>62000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>73300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>63500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>57500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>60400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>51900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>45800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>47200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>43700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>41500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>43100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38600</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5360,50 +5500,53 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>420700</v>
+      </c>
+      <c r="E61" s="3">
         <v>410700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>398600</v>
       </c>
-      <c r="F61" s="3">
-        <v>119700</v>
-      </c>
       <c r="G61" s="3">
+        <v>364800</v>
+      </c>
+      <c r="H61" s="3">
         <v>121400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>123000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>78300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>79900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>80600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>57700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5458,92 +5601,95 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E62" s="3">
         <v>19800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8400</v>
       </c>
-      <c r="F62" s="3">
-        <v>257600</v>
-      </c>
       <c r="G62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>71200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>70400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>74300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>75100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>44900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>47600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>49700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30400</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5556,8 +5702,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,92 +6005,95 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E66" s="3">
         <v>723200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>655000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>564200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>287200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>293100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>196700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>182900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>235500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>146800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>142900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>121000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>126700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>144500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>134000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>131800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>135400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>96800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>89000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>89100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>92700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>93500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>69000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>68000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>69100</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5948,8 +6106,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6258,13 +6426,13 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>305100</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>305100</v>
       </c>
       <c r="AD70" s="3">
-        <v>0</v>
+        <v>305100</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,92 +6547,95 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3322900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2869100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2504200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2199000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1951200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1737800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1386900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1253700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-976200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-867700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-769400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-701300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-644800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-571500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-510300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-452600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-347000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-302700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-265500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-231300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-204100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-142800</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6474,8 +6648,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,92 +6951,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1499900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1631300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1596900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1865400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2078200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2265200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1566300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1618800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1725500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1826200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>837500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>930800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>952200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>685200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>681400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>498800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>551000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>602600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>638200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>685000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>722600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>474700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>505100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>360500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>385300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-152600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-139400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6866,8 +7052,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-453800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-364900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-305200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-247800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-213400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-194600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-156300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-133200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-116000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-161500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-108400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-98300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-68100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-73300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-61200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-57600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-52700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-52900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-44300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-37200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-34200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-27200</v>
       </c>
       <c r="Z81" s="3">
         <v>-27200</v>
       </c>
       <c r="AA81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-43100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,61 +7399,62 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2500</v>
       </c>
       <c r="G83" s="3">
         <v>2500</v>
       </c>
       <c r="H83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2300</v>
       </c>
       <c r="L83" s="3">
         <v>2300</v>
       </c>
       <c r="M83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="N83" s="3">
         <v>2100</v>
       </c>
       <c r="O83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1200</v>
       </c>
       <c r="S83" s="3">
         <v>1200</v>
       </c>
       <c r="T83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
@@ -7264,7 +7463,7 @@
         <v>1100</v>
       </c>
       <c r="W83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>900</v>
@@ -7282,25 +7481,28 @@
         <v>900</v>
       </c>
       <c r="AC83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1100</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-354200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-274200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-207300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-221800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-194400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-138300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-130400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-128200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-160600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-120600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-67100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-62400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-61800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-51700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-55700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-55200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-39300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-36600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-34100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-37200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>13000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>172600</v>
+      </c>
+      <c r="E94" s="3">
         <v>74900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>34300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-392900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>107900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-248000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-380400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>77400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-123400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>62400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>44000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>8500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-30200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-122800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>62900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-136500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>8000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-110000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8392,8 +8626,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8449,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,106 +8986,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>238700</v>
+      </c>
+      <c r="E100" s="3">
         <v>365700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>256600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>873800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>77300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>839400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>64600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>324200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>51400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>248300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>10700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>282300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>168900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>253700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100200</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>4200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>56600</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8882,8 +9131,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8939,102 +9188,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E102" s="3">
         <v>166300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-184100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>69100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-209500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>342600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-74600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-407700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>338400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-46000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>265800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>73200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-66400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-156000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>247300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>39400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>40900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-157800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>166000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-47800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>68300</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
